--- a/Assets/06 Data/ExcelData/dt_shop_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_shop_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A53F0C7-8412-4E33-A363-F4A21E575055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E2AAD3-BB59-4BD2-B944-3742346ACC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="3495" windowWidth="24300" windowHeight="11295" xr2:uid="{B6FC80BC-1448-478E-B3D9-69242C647A71}"/>
+    <workbookView xWindow="3285" yWindow="2400" windowWidth="24300" windowHeight="11295" xr2:uid="{B6FC80BC-1448-478E-B3D9-69242C647A71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>uint</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -55,6 +55,70 @@
   </si>
   <si>
     <t>//슬롯 번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M700</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>글록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S-일반 탄약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 저격탄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지혈 붕대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구급상자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대형 구급상자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코코아 우유</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산수</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -150,7 +214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -166,16 +230,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -512,273 +570,292 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03432785-0241-4416-9435-5F8D756A938F}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>0</v>
       </c>
       <c r="B4" s="1">
         <v>258</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>780</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>254</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="1">
         <v>595</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>622</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="1">
         <v>10</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>16</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>15</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="1">
         <v>105</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="1">
         <v>403</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="1">
         <v>133</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>11</v>
       </c>
       <c r="B15" s="1">
         <v>428</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>12</v>
       </c>
       <c r="B16" s="1">
         <v>106</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/06 Data/ExcelData/dt_shop_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_shop_item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E2AAD3-BB59-4BD2-B944-3742346ACC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E863683-1F25-449F-83FD-633BBEAFC677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2400" windowWidth="24300" windowHeight="11295" xr2:uid="{B6FC80BC-1448-478E-B3D9-69242C647A71}"/>
+    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{B6FC80BC-1448-478E-B3D9-69242C647A71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
-    <t>uint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -119,6 +115,10 @@
   </si>
   <si>
     <t>탄산수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -586,13 +586,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -604,13 +604,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -622,13 +622,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -646,7 +646,7 @@
         <v>258</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -664,7 +664,7 @@
         <v>780</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -682,7 +682,7 @@
         <v>254</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -700,7 +700,7 @@
         <v>595</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -718,7 +718,7 @@
         <v>622</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -736,7 +736,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -754,7 +754,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -772,7 +772,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -790,7 +790,7 @@
         <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -808,7 +808,7 @@
         <v>403</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -826,7 +826,7 @@
         <v>133</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -844,7 +844,7 @@
         <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -855,7 +855,7 @@
         <v>106</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
